--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25419CB0-FBA4-C142-8D68-DE9674F69B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746D9DD3-2BB2-D244-8537-CE438E4552E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,9 +302,6 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>https://us.3t.bike/collections/racemax-italia</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -351,6 +348,9 @@
   </si>
   <si>
     <t>a8:f34</t>
+  </si>
+  <si>
+    <t>https://us.3t.bike/collections/extrema-italia</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -746,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -754,7 +754,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21">
@@ -922,10 +922,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="3">
-        <v>104</v>
+        <v>1044</v>
       </c>
       <c r="D16" s="3">
         <v>1036</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20">
         <v>179</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>637</v>
@@ -1054,7 +1054,7 @@
         <v>196</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1074,7 +1074,7 @@
         <v>61</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1105,7 +1105,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D26">
         <v>1099</v>
@@ -1281,7 +1281,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>73</v>
@@ -1296,7 +1296,7 @@
         <v>76</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1359,7 +1359,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1380,7 +1380,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1391,7 +1391,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1399,10 +1399,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1468,7 +1468,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1476,7 +1476,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1484,7 +1484,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1492,7 +1492,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1500,7 +1500,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1529,7 +1529,7 @@
         <v>66</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746D9DD3-2BB2-D244-8537-CE438E4552E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8A1438-B132-634A-8DE3-10F188EC7C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>https://us.3t.bike/collections/extrema-italia</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -703,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1036,6 +1054,9 @@
       <c r="F21">
         <v>650</v>
       </c>
+      <c r="G21" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
@@ -1054,7 +1075,7 @@
         <v>196</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1073,9 +1094,6 @@
       <c r="F23">
         <v>61</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
@@ -1252,13 +1270,16 @@
       <c r="F36">
         <v>195</v>
       </c>
+      <c r="G36" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="21">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>68</v>
@@ -1273,15 +1294,15 @@
         <v>71</v>
       </c>
       <c r="G37" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="21">
       <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>73</v>
@@ -1295,99 +1316,96 @@
       <c r="F38" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G38" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40">
-        <v>57</v>
+        <v>31</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B43">
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>39</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46">
-        <v>142</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47">
-        <v>100</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="B49">
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B50">
-        <v>27.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52">
         <v>44</v>
       </c>
       <c r="C52" t="s">
@@ -1396,10 +1414,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>45</v>
+      </c>
+      <c r="B53">
+        <v>27.2</v>
       </c>
       <c r="C53" t="s">
         <v>102</v>
@@ -1407,89 +1425,89 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>46</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B55">
-        <v>160</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="B57">
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="B58">
+        <v>160</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>89</v>
+        <v>56</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>89</v>
@@ -1497,38 +1515,62 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68">
-        <v>6399</v>
+        <v>60</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69">
-        <v>9299</v>
+        <v>61</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71">
+        <v>6399</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72">
+        <v>9299</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
         <v>66</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>90</v>
       </c>
     </row>

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8A1438-B132-634A-8DE3-10F188EC7C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CAD220-05C6-4D43-9110-ADE3E97717F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://us.3t.bike/cdn/shop/files/Extrema---selva---1439-Modifica_720x.jpg?v=1759334713</t>
   </si>
 </sst>
 </file>
@@ -767,6 +770,11 @@
         <v>105</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CAD220-05C6-4D43-9110-ADE3E97717F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4A7742-DD96-E249-A7E0-30DD1E8E9B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11060" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -305,9 +305,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>6'0" 6'5"</t>
   </si>
   <si>
@@ -372,6 +369,15 @@
   </si>
   <si>
     <t>https://us.3t.bike/cdn/shop/files/Extrema---selva---1439-Modifica_720x.jpg?v=1759334713</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bergamo, Italy</t>
   </si>
 </sst>
 </file>
@@ -724,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -743,7 +749,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -767,12 +773,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -780,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21">
@@ -948,7 +954,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="3">
         <v>1044</v>
@@ -1025,10 +1031,10 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20">
         <v>179</v>
@@ -1045,10 +1051,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21">
         <v>637</v>
@@ -1063,7 +1069,7 @@
         <v>650</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1083,7 +1089,7 @@
         <v>196</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1131,7 +1137,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D26">
         <v>1099</v>
@@ -1284,10 +1290,10 @@
     </row>
     <row r="37" spans="1:7" ht="21">
       <c r="A37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
         <v>106</v>
-      </c>
-      <c r="B37" t="s">
-        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>68</v>
@@ -1302,15 +1308,15 @@
         <v>71</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="21">
       <c r="A38" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" t="s">
         <v>108</v>
-      </c>
-      <c r="B38" t="s">
-        <v>109</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>73</v>
@@ -1327,10 +1333,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" t="s">
         <v>110</v>
-      </c>
-      <c r="B39" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1409,7 +1415,7 @@
         <v>43</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1417,7 +1423,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1428,7 +1434,7 @@
         <v>27.2</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1452,7 +1458,7 @@
         <v>48</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1534,7 +1540,7 @@
         <v>60</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1550,7 +1556,7 @@
         <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1579,7 +1585,15 @@
         <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>90</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4A7742-DD96-E249-A7E0-30DD1E8E9B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B2C20EC-BA37-B842-9520-AE17CEAA7555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11060" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -326,9 +326,6 @@
     <t>Extrema Italia</t>
   </si>
   <si>
-    <t>48/35</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>Bergamo, Italy</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -773,12 +773,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -786,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21">
@@ -1069,7 +1069,7 @@
         <v>650</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1089,7 +1089,7 @@
         <v>196</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1137,7 +1137,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D26">
         <v>1099</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="37" spans="1:7" ht="21">
       <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
         <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>68</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="38" spans="1:7" ht="21">
       <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
         <v>107</v>
-      </c>
-      <c r="B38" t="s">
-        <v>108</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>73</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" t="s">
         <v>109</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1415,7 +1415,7 @@
         <v>43</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1423,7 +1423,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1434,7 +1434,7 @@
         <v>27.2</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1457,8 +1457,8 @@
       <c r="A56" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>97</v>
+      <c r="B56" s="1">
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1491,7 +1491,9 @@
       <c r="A61" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="1"/>
+      <c r="B61" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
@@ -1540,7 +1542,7 @@
         <v>60</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1556,7 +1558,7 @@
         <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1585,15 +1587,15 @@
         <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" t="s">
         <v>113</v>
-      </c>
-      <c r="B75" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B2C20EC-BA37-B842-9520-AE17CEAA7555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918C0538-0896-E243-9A21-FCAC48310D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -375,9 +375,6 @@
   </si>
   <si>
     <t>Bergamo, Italy</t>
-  </si>
-  <si>
-    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1491,9 +1488,7 @@
       <c r="A61" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918C0538-0896-E243-9A21-FCAC48310D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9570ECC-F054-1946-A4E4-E14C03EDCCDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,24 @@
   </si>
   <si>
     <t>Bergamo, Italy</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -727,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1409,187 +1427,217 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55">
-        <v>44</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="1">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>43</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="C58" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B59">
+        <v>27.2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="B61">
+        <v>44</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B62" s="1">
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B63">
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>99</v>
+        <v>56</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B71">
-        <v>6399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72">
-        <v>9299</v>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77">
+        <v>6399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78">
+        <v>9299</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="1" t="s">
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>113</v>
       </c>
     </row>

--- a/data/gravel/3T Extrema Italia 2025.xlsx
+++ b/data/gravel/3T Extrema Italia 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9570ECC-F054-1946-A4E4-E14C03EDCCDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A7318D-9CB6-814B-8AB1-A96181FF9174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1229,20 +1229,16 @@
         <v>27</v>
       </c>
       <c r="C33">
-        <f>C35</f>
         <v>151</v>
       </c>
       <c r="D33">
-        <f>AVERAGE(D35,C36)</f>
-        <v>169.5</v>
+        <v>168</v>
       </c>
       <c r="E33">
-        <f t="shared" ref="E33:F33" si="1">AVERAGE(E35,D36)</f>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F33">
-        <f t="shared" si="1"/>
-        <v>184.5</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1250,100 +1246,72 @@
         <v>28</v>
       </c>
       <c r="C34">
-        <f>D33</f>
-        <v>169.5</v>
+        <v>171</v>
       </c>
       <c r="D34">
-        <f t="shared" ref="D34:E34" si="2">E33</f>
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E34">
-        <f t="shared" si="2"/>
-        <v>184.5</v>
+        <v>186</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34" si="3">F36</f>
         <v>195</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="C35">
-        <v>151</v>
-      </c>
-      <c r="D35">
-        <v>168</v>
-      </c>
-      <c r="E35">
-        <v>176</v>
-      </c>
-      <c r="F35">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+    <row r="35" spans="1:7" ht="21">
+      <c r="C35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="21">
       <c r="A36" t="s">
         <v>29</v>
       </c>
       <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="C36">
-        <v>171</v>
-      </c>
-      <c r="D36">
-        <v>180</v>
-      </c>
-      <c r="E36">
-        <v>186</v>
-      </c>
-      <c r="F36">
-        <v>195</v>
-      </c>
-      <c r="G36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="21">
+      <c r="C36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>104</v>
       </c>
       <c r="B37" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="21">
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>106</v>
       </c>
       <c r="B38" t="s">
         <v>107</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:7">
